--- a/Tarreessa.xlsx
+++ b/Tarreessa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\Tarreessa\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,86 +24,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
-  <si>
-    <t>Maqaa</t>
-  </si>
-  <si>
-    <t>Lakk</t>
-  </si>
-  <si>
-    <t>Lakk.Bilbilaa</t>
-  </si>
-  <si>
-    <t>Amma maallaqaa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Tasfaayee Alamuu</t>
   </si>
   <si>
-    <t>Tasfaayee Damisee</t>
-  </si>
-  <si>
-    <t>Biraanuu Tasfaayee</t>
-  </si>
-  <si>
     <t>Kabbadaa Nagaraa</t>
   </si>
   <si>
     <t>Tarreessaa Wadaajoo</t>
   </si>
   <si>
-    <t>Fiqaaduu Ajjamaa</t>
-  </si>
-  <si>
-    <t>Warqinaa dhe fi Taammiraat Diribsaa</t>
-  </si>
-  <si>
     <t>Girmaa Baqqalaa</t>
   </si>
   <si>
-    <t>Ajjamaa Gaaddisaa</t>
-  </si>
-  <si>
-    <t>Naggessaa Biqilaa</t>
-  </si>
-  <si>
     <t>Magarsaa Fufaa</t>
   </si>
   <si>
-    <t>Caaluu Baqqalaa</t>
-  </si>
-  <si>
-    <t>Dhufeeraa Addunnaa</t>
-  </si>
-  <si>
     <t>Daagim Guddisaa</t>
   </si>
   <si>
     <t>Maammoo Taaddasaa</t>
   </si>
   <si>
-    <t>Magarsaa Ida`ee</t>
-  </si>
-  <si>
-    <t>Bashaadaa Abdataa</t>
-  </si>
-  <si>
     <t>Xannaa Dirribaa</t>
   </si>
   <si>
     <t>Dajanee Guutaa</t>
   </si>
   <si>
-    <t>Atoomsaa Kafanaa fi Misgee Birruu</t>
-  </si>
-  <si>
-    <t>Balaayinash Fufaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mokonnoon Dinqeessaa </t>
-  </si>
-  <si>
     <t>Taaddasaa Moosisaa</t>
   </si>
   <si>
@@ -113,70 +62,163 @@
     <t>Balaay Kumalaa</t>
   </si>
   <si>
-    <t>Wasanaa Warquu</t>
-  </si>
-  <si>
-    <t>siste Margaa Alamuu</t>
-  </si>
-  <si>
-    <t>Alamaayyoo Magarsaa</t>
-  </si>
-  <si>
-    <t>Biraanuu Jamamaa</t>
-  </si>
-  <si>
-    <t>Daani`eel Tarreessaa</t>
-  </si>
-  <si>
-    <t>Bareechaa Abdataa</t>
-  </si>
-  <si>
-    <t>Siinan Giddumaa</t>
-  </si>
-  <si>
-    <t>Geetuu Kabbadaa</t>
-  </si>
-  <si>
     <t>Shimallis Gonfaa</t>
   </si>
   <si>
     <t>Damisee Zawuduu</t>
   </si>
   <si>
-    <t>Abbabaa Ajjamaa</t>
-  </si>
-  <si>
-    <t>Bizaayyoo Mullallataa</t>
-  </si>
-  <si>
-    <t>Sisaayi Nugusee</t>
-  </si>
-  <si>
-    <t>Leellisaa Doojji</t>
-  </si>
-  <si>
     <t>Mootummaa Tamasgeen</t>
   </si>
   <si>
-    <t xml:space="preserve">Tasammaa Kaasayee </t>
-  </si>
-  <si>
-    <t>Zamanuu Dhaabaa fi Damisee</t>
-  </si>
-  <si>
-    <t>Luluu Asfaawu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayyisaa Biraanuu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taaffasaa Taammiruu </t>
-  </si>
-  <si>
     <t>Alamuu Guutaa</t>
   </si>
   <si>
-    <t>Lammii, Qananiisaa fi Walfaanaa</t>
+    <t>Lak k.</t>
+  </si>
+  <si>
+    <t>Maqaa miseensotaa</t>
+  </si>
+  <si>
+    <t>Hamma Maallaqaa</t>
+  </si>
+  <si>
+    <t>Biranuu Tasfaayee</t>
+  </si>
+  <si>
+    <t>Fiqaaduu Ajiamaa</t>
+  </si>
+  <si>
+    <t>Warqinaa Dheereessaa fi Taanmiraat Dirribsa</t>
+  </si>
+  <si>
+    <t>Caalaa Cawwaaqaa</t>
+  </si>
+  <si>
+    <t>Tasfaayee Damisee Qarshii</t>
+  </si>
+  <si>
+    <t>Guddisaa Badhaanee</t>
+  </si>
+  <si>
+    <t>Ajiamaa Gaaddisaa</t>
+  </si>
+  <si>
+    <t>Nageessaa Biqilaa</t>
+  </si>
+  <si>
+    <t>Caalu Baaqqalaa</t>
+  </si>
+  <si>
+    <t>Dhufeeraa Addunaa</t>
+  </si>
+  <si>
+    <t>Dajanee Bashaan aa</t>
+  </si>
+  <si>
+    <t>Magarsaa Ida'ee</t>
+  </si>
+  <si>
+    <t>Bashaaedaa Abdalaa</t>
+  </si>
+  <si>
+    <t>Atoomsaa Kafanaa fi Misgaanaa Birruu</t>
+  </si>
+  <si>
+    <t>Balaayiinaash Fufaa</t>
+  </si>
+  <si>
+    <t>Mokonniin Dingessaa</t>
+  </si>
+  <si>
+    <t>Lulun Astaw</t>
+  </si>
+  <si>
+    <t>Walfaanaa Magarsaa, Qamaniiisaa Biqilaa fi Lammi Diroo</t>
+  </si>
+  <si>
+    <t>Lalisa Tararaa</t>
+  </si>
+  <si>
+    <t>Tolanaa Nuuriisaa</t>
+  </si>
+  <si>
+    <t>Molalan Siimaa</t>
+  </si>
+  <si>
+    <t>Tuutuu Taaddasaa</t>
+  </si>
+  <si>
+    <t>Wasanaa Waarquu</t>
+  </si>
+  <si>
+    <t>Alamaayoo Magarsaa</t>
+  </si>
+  <si>
+    <t>Shibirruu Fayyee</t>
+  </si>
+  <si>
+    <t>Birhaanuu Jamaa</t>
+  </si>
+  <si>
+    <t>Da'aa Ertiraam</t>
+  </si>
+  <si>
+    <t>Sinnaa Dirribaa</t>
+  </si>
+  <si>
+    <t>Buzayinoo Mul'ataa</t>
+  </si>
+  <si>
+    <t>Sisaay Nugusee</t>
+  </si>
+  <si>
+    <t>Leellisaaa Doojjii</t>
+  </si>
+  <si>
+    <t>Tasfaamraa Kaasayee</t>
+  </si>
+  <si>
+    <t>Taaffasaa Taammiiruu</t>
+  </si>
+  <si>
+    <t>Birhaanuu Tasfaayee</t>
+  </si>
+  <si>
+    <t>Fayyyee Jootee</t>
+  </si>
+  <si>
+    <t>Hayiluu Garaajii</t>
+  </si>
+  <si>
+    <t>Abbaabuu Ajiamaa</t>
+  </si>
+  <si>
+    <t>Balaayi Kumalaa</t>
+  </si>
+  <si>
+    <t>Geetuu Kabbabaa</t>
+  </si>
+  <si>
+    <t>Bareecha Abdataa</t>
+  </si>
+  <si>
+    <t>Zabanuu Dhaabaa</t>
+  </si>
+  <si>
+    <t>Fayisaa Biiranuu</t>
+  </si>
+  <si>
+    <t>Dargee Faananaa</t>
+  </si>
+  <si>
+    <t>Kumsaa Galataa</t>
+  </si>
+  <si>
+    <t>Aangaasaa</t>
+  </si>
+  <si>
+    <t>Paastor Margaa Alamuu</t>
   </si>
 </sst>
 </file>
@@ -494,675 +536,704 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>911383348</v>
-      </c>
-      <c r="D2">
         <v>100000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>911436280</v>
-      </c>
-      <c r="D3">
         <v>100000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>911825646</v>
-      </c>
-      <c r="D4">
         <v>100000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>911822021</v>
-      </c>
-      <c r="D5">
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>913952050</v>
-      </c>
-      <c r="D6">
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>911069937</v>
-      </c>
-      <c r="D7">
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>921597788</v>
-      </c>
-      <c r="D8">
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C9">
-        <v>910139493</v>
-      </c>
-      <c r="D9">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>913079768</v>
-      </c>
-      <c r="D10">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C11">
-        <v>911706422</v>
-      </c>
-      <c r="D11">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>919475159</v>
-      </c>
-      <c r="D12">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>914218365</v>
-      </c>
-      <c r="D13">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C14">
-        <v>925911915</v>
-      </c>
-      <c r="D14">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>947270061</v>
-      </c>
-      <c r="D16">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>911405163</v>
-      </c>
-      <c r="D17">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>919669888</v>
-      </c>
-      <c r="D18">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C19">
-        <v>910164278</v>
-      </c>
-      <c r="D19">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C20">
-        <v>913216895</v>
-      </c>
-      <c r="D20">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>979757957</v>
-      </c>
-      <c r="D21">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>917854425</v>
-      </c>
-      <c r="D22">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C23">
-        <v>9</v>
-      </c>
-      <c r="D23">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C24">
-        <v>933274832</v>
-      </c>
-      <c r="D24">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>913934897</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C29">
-        <v>911975541</v>
-      </c>
-      <c r="D29">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>922969728</v>
-      </c>
-      <c r="D30">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C31">
-        <v>911801878</v>
-      </c>
-      <c r="D31">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C32">
-        <v>913117355</v>
-      </c>
-      <c r="D32">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>961111137</v>
-      </c>
-      <c r="D33">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>910108406</v>
-      </c>
-      <c r="D34">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C35">
-        <v>955349811</v>
-      </c>
-      <c r="D35">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C36">
-        <v>911584940</v>
-      </c>
-      <c r="D36">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C37">
-        <v>913710490</v>
-      </c>
-      <c r="D37">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>938966504</v>
-      </c>
-      <c r="D38">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="C39">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>911819348</v>
-      </c>
-      <c r="D40">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="C41">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C42">
-        <v>912766225</v>
-      </c>
-      <c r="D42">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>911033023</v>
-      </c>
-      <c r="D43">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C44">
-        <v>920927937</v>
-      </c>
-      <c r="D44">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C45">
-        <v>911544058</v>
-      </c>
-      <c r="D45">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C46">
-        <v>967989190</v>
-      </c>
-      <c r="D46">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="C47">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>942148848</v>
-      </c>
-      <c r="D48">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="C49">
-        <v>912861288</v>
-      </c>
-      <c r="D49">
-        <v>50000</v>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/Tarreessa.xlsx
+++ b/Tarreessa.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Tasfaayee Alamuu</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Tasammaa Tasfaayee</t>
   </si>
   <si>
-    <t>Balaay Kumalaa</t>
-  </si>
-  <si>
     <t>Shimallis Gonfaa</t>
   </si>
   <si>
@@ -86,24 +83,15 @@
     <t>Biranuu Tasfaayee</t>
   </si>
   <si>
-    <t>Fiqaaduu Ajiamaa</t>
-  </si>
-  <si>
     <t>Warqinaa Dheereessaa fi Taanmiraat Dirribsa</t>
   </si>
   <si>
     <t>Caalaa Cawwaaqaa</t>
   </si>
   <si>
-    <t>Tasfaayee Damisee Qarshii</t>
-  </si>
-  <si>
     <t>Guddisaa Badhaanee</t>
   </si>
   <si>
-    <t>Ajiamaa Gaaddisaa</t>
-  </si>
-  <si>
     <t>Nageessaa Biqilaa</t>
   </si>
   <si>
@@ -113,72 +101,24 @@
     <t>Dhufeeraa Addunaa</t>
   </si>
   <si>
-    <t>Dajanee Bashaan aa</t>
-  </si>
-  <si>
     <t>Magarsaa Ida'ee</t>
   </si>
   <si>
-    <t>Bashaaedaa Abdalaa</t>
-  </si>
-  <si>
     <t>Atoomsaa Kafanaa fi Misgaanaa Birruu</t>
   </si>
   <si>
-    <t>Balaayiinaash Fufaa</t>
-  </si>
-  <si>
-    <t>Mokonniin Dingessaa</t>
-  </si>
-  <si>
-    <t>Lulun Astaw</t>
-  </si>
-  <si>
-    <t>Walfaanaa Magarsaa, Qamaniiisaa Biqilaa fi Lammi Diroo</t>
-  </si>
-  <si>
-    <t>Lalisa Tararaa</t>
-  </si>
-  <si>
-    <t>Tolanaa Nuuriisaa</t>
-  </si>
-  <si>
-    <t>Molalan Siimaa</t>
-  </si>
-  <si>
-    <t>Tuutuu Taaddasaa</t>
-  </si>
-  <si>
     <t>Wasanaa Waarquu</t>
   </si>
   <si>
     <t>Alamaayoo Magarsaa</t>
   </si>
   <si>
-    <t>Shibirruu Fayyee</t>
-  </si>
-  <si>
-    <t>Birhaanuu Jamaa</t>
-  </si>
-  <si>
-    <t>Da'aa Ertiraam</t>
-  </si>
-  <si>
-    <t>Sinnaa Dirribaa</t>
-  </si>
-  <si>
-    <t>Buzayinoo Mul'ataa</t>
-  </si>
-  <si>
     <t>Sisaay Nugusee</t>
   </si>
   <si>
     <t>Leellisaaa Doojjii</t>
   </si>
   <si>
-    <t>Tasfaamraa Kaasayee</t>
-  </si>
-  <si>
     <t>Taaffasaa Taammiiruu</t>
   </si>
   <si>
@@ -191,9 +131,6 @@
     <t>Hayiluu Garaajii</t>
   </si>
   <si>
-    <t>Abbaabuu Ajiamaa</t>
-  </si>
-  <si>
     <t>Balaayi Kumalaa</t>
   </si>
   <si>
@@ -206,19 +143,79 @@
     <t>Zabanuu Dhaabaa</t>
   </si>
   <si>
-    <t>Fayisaa Biiranuu</t>
-  </si>
-  <si>
-    <t>Dargee Faananaa</t>
-  </si>
-  <si>
     <t>Kumsaa Galataa</t>
   </si>
   <si>
     <t>Aangaasaa</t>
   </si>
   <si>
-    <t>Paastor Margaa Alamuu</t>
+    <t>Fiqaaduu Ajjamaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasfaayee Damisee </t>
+  </si>
+  <si>
+    <t>Ajjamaa Gaaddisaa</t>
+  </si>
+  <si>
+    <t>Dajanee Bashaanaa</t>
+  </si>
+  <si>
+    <t>Bashaadaa Abdalaa</t>
+  </si>
+  <si>
+    <t>Balaayinaash Fufaa</t>
+  </si>
+  <si>
+    <t>Mokonniin Dinqeessaa</t>
+  </si>
+  <si>
+    <t>Luluu Asfaaw</t>
+  </si>
+  <si>
+    <t>Walfaanaa Magarsaa, Qananiiisaa Biqilaa fi Lammi Diroo</t>
+  </si>
+  <si>
+    <t>Lalisa Taraaraa</t>
+  </si>
+  <si>
+    <t>Tolasaa Nuurasaa</t>
+  </si>
+  <si>
+    <t>Mollaa Simaa</t>
+  </si>
+  <si>
+    <t>Biraanuu Taaddasaa</t>
+  </si>
+  <si>
+    <t>Shibirruu Fayyeeraa</t>
+  </si>
+  <si>
+    <t>Birhaanuu Jamaamaa</t>
+  </si>
+  <si>
+    <t>Daani`el Tarreessaa</t>
+  </si>
+  <si>
+    <t>Sinan Giddumaa</t>
+  </si>
+  <si>
+    <t>Buzaayyoo Mul'ataa</t>
+  </si>
+  <si>
+    <t>Tasaammaa Kaasayee</t>
+  </si>
+  <si>
+    <t>Abbaabuu Ajjamaa</t>
+  </si>
+  <si>
+    <t>Fayisaa Biraanuu</t>
+  </si>
+  <si>
+    <t>Darajjee Faanaa</t>
+  </si>
+  <si>
+    <t>Paastar Margaa Alamuu</t>
   </si>
 </sst>
 </file>
@@ -536,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
@@ -545,13 +542,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>100000</v>
@@ -603,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>100000</v>
@@ -625,7 +622,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>100000</v>
@@ -636,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>100000</v>
@@ -647,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C10">
         <v>100000</v>
@@ -658,7 +655,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>100000</v>
@@ -680,7 +677,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>50000</v>
@@ -691,7 +688,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>50000</v>
@@ -702,7 +699,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>50000</v>
@@ -713,7 +710,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>50000</v>
@@ -746,7 +743,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>50000</v>
@@ -757,7 +754,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>50000</v>
@@ -768,7 +765,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>50000</v>
@@ -790,7 +787,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>50000</v>
@@ -801,7 +798,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>50000</v>
@@ -812,7 +809,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>50000</v>
@@ -834,7 +831,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>50000</v>
@@ -856,7 +853,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>50000</v>
@@ -867,7 +864,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>50000</v>
@@ -878,7 +875,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>50000</v>
@@ -889,7 +886,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>50000</v>
@@ -900,7 +897,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>30000</v>
@@ -911,7 +908,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>30000</v>
@@ -922,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C35">
         <v>25000</v>
@@ -933,7 +930,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C36">
         <v>25000</v>
@@ -944,7 +941,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>25000</v>
@@ -955,7 +952,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>25000</v>
@@ -966,7 +963,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C39">
         <v>25000</v>
@@ -977,7 +974,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C40">
         <v>25000</v>
@@ -988,7 +985,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>25000</v>
@@ -999,7 +996,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>25000</v>
@@ -1010,7 +1007,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C43">
         <v>25000</v>
@@ -1021,7 +1018,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44">
         <v>25000</v>
@@ -1032,7 +1029,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C45">
         <v>25000</v>
@@ -1043,7 +1040,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C46">
         <v>25000</v>
@@ -1054,7 +1051,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C47">
         <v>25000</v>
@@ -1065,7 +1062,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48">
         <v>25000</v>
@@ -1076,7 +1073,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C49">
         <v>25000</v>
@@ -1098,7 +1095,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51">
         <v>25000</v>
@@ -1109,7 +1106,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C52">
         <v>25000</v>
@@ -1120,7 +1117,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C53">
         <v>20000</v>
@@ -1131,7 +1128,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C54">
         <v>15000</v>
@@ -1142,7 +1139,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C55">
         <v>15000</v>
@@ -1150,21 +1147,21 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C56">
-        <v>15000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C57">
         <v>12500</v>
@@ -1172,10 +1169,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>12500</v>
@@ -1183,10 +1180,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>12500</v>
@@ -1194,10 +1191,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C60">
         <v>12500</v>
@@ -1205,10 +1202,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C61">
         <v>12500</v>
@@ -1216,23 +1213,12 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
       </c>
       <c r="C62">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63">
         <v>10000</v>
       </c>
     </row>

--- a/Tarreessa.xlsx
+++ b/Tarreessa.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Tasfaayee Alamuu</t>
   </si>
@@ -216,13 +216,50 @@
   </si>
   <si>
     <t>Paastar Margaa Alamuu</t>
+  </si>
+  <si>
+    <t>Hiwoot Zallaqaa</t>
+  </si>
+  <si>
+    <t>Abdiisaa Lallisaa</t>
+  </si>
+  <si>
+    <t>Darajjee Tashoomaa</t>
+  </si>
+  <si>
+    <t>Lalisaa Baay`isaa</t>
+  </si>
+  <si>
+    <t>Dawwit Lammessaa</t>
+  </si>
+  <si>
+    <t>Caalumaa Barsiisaa</t>
+  </si>
+  <si>
+    <t>Xilahuun fi Tolasaa</t>
+  </si>
+  <si>
+    <t>Taaddaluu Toleeraa</t>
+  </si>
+  <si>
+    <t>Bokonaa Uggumaa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,13 +285,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -533,11 +573,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -547,7 +587,7 @@
       <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -558,7 +598,7 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -569,7 +609,7 @@
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -580,7 +620,7 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -591,7 +631,7 @@
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -602,7 +642,7 @@
       <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -613,7 +653,7 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -624,7 +664,7 @@
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -635,7 +675,7 @@
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -646,7 +686,7 @@
       <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -657,7 +697,7 @@
       <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>100000</v>
       </c>
     </row>
@@ -668,7 +708,7 @@
       <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -679,7 +719,7 @@
       <c r="B13" t="s">
         <v>43</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -690,7 +730,7 @@
       <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -701,7 +741,7 @@
       <c r="B15" t="s">
         <v>23</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -712,7 +752,7 @@
       <c r="B16" t="s">
         <v>24</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -723,7 +763,7 @@
       <c r="B17" t="s">
         <v>5</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -734,7 +774,7 @@
       <c r="B18" t="s">
         <v>6</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -745,7 +785,7 @@
       <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -756,7 +796,7 @@
       <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -767,7 +807,7 @@
       <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -778,7 +818,7 @@
       <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -789,7 +829,7 @@
       <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -800,7 +840,7 @@
       <c r="B24" t="s">
         <v>46</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -811,7 +851,7 @@
       <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -822,7 +862,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -833,7 +873,7 @@
       <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -844,7 +884,7 @@
       <c r="B28" t="s">
         <v>8</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -855,7 +895,7 @@
       <c r="B29" t="s">
         <v>49</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -866,7 +906,7 @@
       <c r="B30" t="s">
         <v>50</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -877,7 +917,7 @@
       <c r="B31" t="s">
         <v>51</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -888,7 +928,7 @@
       <c r="B32" t="s">
         <v>52</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>50000</v>
       </c>
     </row>
@@ -899,330 +939,432 @@
       <c r="B33" t="s">
         <v>53</v>
       </c>
-      <c r="C33">
-        <v>30000</v>
+      <c r="C33" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34">
-        <v>30000</v>
+        <v>67</v>
+      </c>
+      <c r="C34" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35">
-        <v>25000</v>
+        <v>68</v>
+      </c>
+      <c r="C35" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36">
-        <v>25000</v>
+        <v>69</v>
+      </c>
+      <c r="C36" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37">
-        <v>25000</v>
+        <v>70</v>
+      </c>
+      <c r="C37" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38">
-        <v>25000</v>
+        <v>71</v>
+      </c>
+      <c r="C38" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39">
-        <v>25000</v>
+        <v>72</v>
+      </c>
+      <c r="C39" s="1">
+        <v>50000</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40">
-        <v>25000</v>
+        <v>12</v>
+      </c>
+      <c r="C40" s="1">
+        <v>30000</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41">
+        <v>27</v>
+      </c>
+      <c r="C41" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42">
+        <v>28</v>
+      </c>
+      <c r="C42" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43">
+        <v>54</v>
+      </c>
+      <c r="C43" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44">
+        <v>55</v>
+      </c>
+      <c r="C44" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45">
+        <v>56</v>
+      </c>
+      <c r="C45" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46">
+        <v>57</v>
+      </c>
+      <c r="C46" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47">
+        <v>58</v>
+      </c>
+      <c r="C47" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48">
+        <v>29</v>
+      </c>
+      <c r="C48" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49">
+        <v>30</v>
+      </c>
+      <c r="C49" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51">
+        <v>59</v>
+      </c>
+      <c r="C51" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52">
+        <v>31</v>
+      </c>
+      <c r="C52" s="1">
         <v>25000</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53">
-        <v>20000</v>
+        <v>32</v>
+      </c>
+      <c r="C53" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54">
-        <v>15000</v>
+        <v>14</v>
+      </c>
+      <c r="C54" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55">
-        <v>15000</v>
+        <v>33</v>
+      </c>
+      <c r="C55" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56">
-        <v>12500</v>
+        <v>10</v>
+      </c>
+      <c r="C56" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
-      </c>
-      <c r="C57">
-        <v>12500</v>
+        <v>11</v>
+      </c>
+      <c r="C57" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58">
-        <v>12500</v>
+        <v>34</v>
+      </c>
+      <c r="C58" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59">
-        <v>12500</v>
+        <v>64</v>
+      </c>
+      <c r="C59" s="1">
+        <v>25000</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
+        <v>52</v>
+      </c>
+      <c r="B60" t="s">
         <v>60</v>
       </c>
-      <c r="B60" t="s">
-        <v>39</v>
-      </c>
-      <c r="C60">
-        <v>12500</v>
+      <c r="C60" s="1">
+        <v>20000</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61">
-        <v>12500</v>
+        <v>35</v>
+      </c>
+      <c r="C61" s="1">
+        <v>15000</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
+        <v>54</v>
+      </c>
+      <c r="B62" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>56</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>57</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>58</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
         <v>62</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C66" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>60</v>
+      </c>
+      <c r="B67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>61</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>65</v>
+      </c>
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" s="1">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>62</v>
+      </c>
+      <c r="B71" t="s">
         <v>63</v>
       </c>
-      <c r="C62">
+      <c r="C71" s="1">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:C71">
+    <sortCondition descending="1" ref="C2:C71"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>